--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/165.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/165.xlsx
@@ -426,13 +426,13 @@
         <v>-16.08777746405865</v>
       </c>
       <c r="E2">
-        <v>-3.868428355389967</v>
+        <v>-5.882711707897772</v>
       </c>
       <c r="F2">
-        <v>-5.079433918145087</v>
+        <v>-3.892894532620923</v>
       </c>
       <c r="G2">
-        <v>-1.45867055236323</v>
+        <v>-4.572669002967886</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.28278925351526</v>
       </c>
       <c r="E3">
-        <v>-4.375649143567101</v>
+        <v>-6.232817090378783</v>
       </c>
       <c r="F3">
-        <v>-4.207254991778918</v>
+        <v>-4.041815939194009</v>
       </c>
       <c r="G3">
-        <v>-2.317628008528071</v>
+        <v>-4.963310066056347</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.30133899931981</v>
       </c>
       <c r="E4">
-        <v>-4.183238811455194</v>
+        <v>-6.541151828613042</v>
       </c>
       <c r="F4">
-        <v>-3.997823003166133</v>
+        <v>-3.892232667066086</v>
       </c>
       <c r="G4">
-        <v>-2.141940667304489</v>
+        <v>-4.333190759748087</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.1224577869773</v>
       </c>
       <c r="E5">
-        <v>-7.110236100208961</v>
+        <v>-7.699789074319549</v>
       </c>
       <c r="F5">
-        <v>-4.048167032071273</v>
+        <v>-3.472028391382787</v>
       </c>
       <c r="G5">
-        <v>-2.181183874127009</v>
+        <v>-3.715975959951906</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.75205071350913</v>
       </c>
       <c r="E6">
-        <v>-8.406742737078991</v>
+        <v>-8.987225177752217</v>
       </c>
       <c r="F6">
-        <v>-4.714019519217753</v>
+        <v>-3.763576440635086</v>
       </c>
       <c r="G6">
-        <v>-1.643918749104227</v>
+        <v>-4.846437876883456</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.21918520210521</v>
       </c>
       <c r="E7">
-        <v>-6.235651915107584</v>
+        <v>-10.05907421910172</v>
       </c>
       <c r="F7">
-        <v>-4.464661878524836</v>
+        <v>-3.921449185362825</v>
       </c>
       <c r="G7">
-        <v>-1.844709957152103</v>
+        <v>-4.858481641555325</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.55804331460685</v>
       </c>
       <c r="E8">
-        <v>-9.233343211595093</v>
+        <v>-10.85793326184683</v>
       </c>
       <c r="F8">
-        <v>-3.876995677058992</v>
+        <v>-3.709165956149604</v>
       </c>
       <c r="G8">
-        <v>-1.331125164371728</v>
+        <v>-4.71255279418425</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.78808513109285</v>
       </c>
       <c r="E9">
-        <v>-10.51079402984085</v>
+        <v>-11.30239392875166</v>
       </c>
       <c r="F9">
-        <v>-4.477496603063813</v>
+        <v>-3.804626187280816</v>
       </c>
       <c r="G9">
-        <v>-1.400491025056078</v>
+        <v>-3.69333513900883</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.93957001355218</v>
       </c>
       <c r="E10">
-        <v>-10.90952616621622</v>
+        <v>-12.5676133387027</v>
       </c>
       <c r="F10">
-        <v>-3.794037995138233</v>
+        <v>-3.711083626687084</v>
       </c>
       <c r="G10">
-        <v>-1.302916005831599</v>
+        <v>-2.84886463012384</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.05503821427501</v>
       </c>
       <c r="E11">
-        <v>-12.25968616312913</v>
+        <v>-15.36661783810367</v>
       </c>
       <c r="F11">
-        <v>-4.526944338439123</v>
+        <v>-3.724861861697849</v>
       </c>
       <c r="G11">
-        <v>-0.4019973849564949</v>
+        <v>-3.495827992135911</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.16301482238202</v>
       </c>
       <c r="E12">
-        <v>-12.8036509894045</v>
+        <v>-13.91779597798565</v>
       </c>
       <c r="F12">
-        <v>-3.759965587126283</v>
+        <v>-3.579374038009366</v>
       </c>
       <c r="G12">
-        <v>0.393705477589492</v>
+        <v>-2.746188060223344</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.2846569351436</v>
       </c>
       <c r="E13">
-        <v>-13.13639873101411</v>
+        <v>-15.51306868751173</v>
       </c>
       <c r="F13">
-        <v>-3.358036753083546</v>
+        <v>-3.614318716896463</v>
       </c>
       <c r="G13">
-        <v>0.2516665212270617</v>
+        <v>-1.814080789822766</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.468477647751577</v>
       </c>
       <c r="E14">
-        <v>-15.55667336373159</v>
+        <v>-16.37263192432966</v>
       </c>
       <c r="F14">
-        <v>-4.068271508937217</v>
+        <v>-3.727982321704194</v>
       </c>
       <c r="G14">
-        <v>0.6461180222312236</v>
+        <v>-0.9736458359501471</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.740220457887624</v>
       </c>
       <c r="E15">
-        <v>-17.21443901456352</v>
+        <v>-17.80204474485081</v>
       </c>
       <c r="F15">
-        <v>-3.940055973964507</v>
+        <v>-3.736767986378286</v>
       </c>
       <c r="G15">
-        <v>1.017405636097105</v>
+        <v>0.1601100737929778</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.108465190805926</v>
       </c>
       <c r="E16">
-        <v>-17.52980194445768</v>
+        <v>-18.60481638913855</v>
       </c>
       <c r="F16">
-        <v>-3.679763883554638</v>
+        <v>-3.356433033791727</v>
       </c>
       <c r="G16">
-        <v>3.257780913797949</v>
+        <v>0.2101920067110723</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.59913493431711</v>
       </c>
       <c r="E17">
-        <v>-16.44026468363422</v>
+        <v>-19.71419289458962</v>
       </c>
       <c r="F17">
-        <v>-3.419488360492825</v>
+        <v>-2.956321637830732</v>
       </c>
       <c r="G17">
-        <v>3.972557490636452</v>
+        <v>0.9893288993785462</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.216918736500843</v>
       </c>
       <c r="E18">
-        <v>-18.2125327997501</v>
+        <v>-20.38206129818886</v>
       </c>
       <c r="F18">
-        <v>-3.682413002508791</v>
+        <v>-3.01445314868959</v>
       </c>
       <c r="G18">
-        <v>3.724624114109354</v>
+        <v>1.006659605276631</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.943566623185122</v>
       </c>
       <c r="E19">
-        <v>-19.72450422990509</v>
+        <v>-21.29972485652521</v>
       </c>
       <c r="F19">
-        <v>-3.829560046105081</v>
+        <v>-3.154559897729487</v>
       </c>
       <c r="G19">
-        <v>4.166856718881817</v>
+        <v>2.124038246236981</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.771619105523714</v>
       </c>
       <c r="E20">
-        <v>-18.87716787290786</v>
+        <v>-22.13056398271248</v>
       </c>
       <c r="F20">
-        <v>-3.331995367041738</v>
+        <v>-2.626392841704522</v>
       </c>
       <c r="G20">
-        <v>5.011115352852294</v>
+        <v>2.474164853015841</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.687846540582268</v>
       </c>
       <c r="E21">
-        <v>-21.54643612046308</v>
+        <v>-22.58327100078528</v>
       </c>
       <c r="F21">
-        <v>-3.482159324719024</v>
+        <v>-2.787545921347347</v>
       </c>
       <c r="G21">
-        <v>4.366873259273503</v>
+        <v>2.960255565092569</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.66403525142386</v>
       </c>
       <c r="E22">
-        <v>-20.74247801598534</v>
+        <v>-23.77092217945894</v>
       </c>
       <c r="F22">
-        <v>-2.760500554013345</v>
+        <v>-2.467297426690252</v>
       </c>
       <c r="G22">
-        <v>5.28849272140567</v>
+        <v>2.873767562879109</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.67794820567481</v>
       </c>
       <c r="E23">
-        <v>-23.44951373676453</v>
+        <v>-24.19581078170261</v>
       </c>
       <c r="F23">
-        <v>-2.725444873894273</v>
+        <v>-2.386353505925698</v>
       </c>
       <c r="G23">
-        <v>5.420752326245093</v>
+        <v>4.054794752377488</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.719499776589397</v>
       </c>
       <c r="E24">
-        <v>-22.31381321190688</v>
+        <v>-24.25454961805611</v>
       </c>
       <c r="F24">
-        <v>-2.541606124558382</v>
+        <v>-2.151290173135491</v>
       </c>
       <c r="G24">
-        <v>4.74699340863816</v>
+        <v>3.820444544198019</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.769170601867234</v>
       </c>
       <c r="E25">
-        <v>-22.81679987688684</v>
+        <v>-24.8325368695511</v>
       </c>
       <c r="F25">
-        <v>-1.883951989597409</v>
+        <v>-2.442510188896283</v>
       </c>
       <c r="G25">
-        <v>4.492730269039976</v>
+        <v>3.815194018972735</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.807277560728908</v>
       </c>
       <c r="E26">
-        <v>-22.59043051819141</v>
+        <v>-24.90796766109687</v>
       </c>
       <c r="F26">
-        <v>-2.139885210733747</v>
+        <v>-2.407733668591954</v>
       </c>
       <c r="G26">
-        <v>5.249878518235611</v>
+        <v>3.907968747165271</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.835969600823335</v>
       </c>
       <c r="E27">
-        <v>-21.89233455059097</v>
+        <v>-24.57790983304782</v>
       </c>
       <c r="F27">
-        <v>-2.341101451445567</v>
+        <v>-2.541998770707309</v>
       </c>
       <c r="G27">
-        <v>4.870758153623814</v>
+        <v>3.877644150025547</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.850569205131583</v>
       </c>
       <c r="E28">
-        <v>-23.38744194354139</v>
+        <v>-25.28995350059188</v>
       </c>
       <c r="F28">
-        <v>-1.868620565706396</v>
+        <v>-2.058352320745803</v>
       </c>
       <c r="G28">
-        <v>4.220494177709089</v>
+        <v>3.484662531240821</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.842758460554606</v>
       </c>
       <c r="E29">
-        <v>-22.10344748035455</v>
+        <v>-24.29672782496355</v>
       </c>
       <c r="F29">
-        <v>-2.517368922719871</v>
+        <v>-2.225417458542408</v>
       </c>
       <c r="G29">
-        <v>5.597710916955756</v>
+        <v>3.01812059057349</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.824297285912024</v>
       </c>
       <c r="E30">
-        <v>-22.23687896699056</v>
+        <v>-22.5356359826986</v>
       </c>
       <c r="F30">
-        <v>-2.622766249215066</v>
+        <v>-2.221554781343154</v>
       </c>
       <c r="G30">
-        <v>4.515708765628058</v>
+        <v>4.104224507824346</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.803672960654571</v>
       </c>
       <c r="E31">
-        <v>-22.76661532793383</v>
+        <v>-23.72908813657607</v>
       </c>
       <c r="F31">
-        <v>-2.253911640463905</v>
+        <v>-2.338917046604385</v>
       </c>
       <c r="G31">
-        <v>4.182187855274182</v>
+        <v>3.50424771865115</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.780973061120466</v>
       </c>
       <c r="E32">
-        <v>-22.59696510618448</v>
+        <v>-22.51511293849584</v>
       </c>
       <c r="F32">
-        <v>-2.351898392173656</v>
+        <v>-2.459852888841293</v>
       </c>
       <c r="G32">
-        <v>5.504502507297576</v>
+        <v>3.364642013260084</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.769280274334191</v>
       </c>
       <c r="E33">
-        <v>-20.26995892412898</v>
+        <v>-23.04565083933846</v>
       </c>
       <c r="F33">
-        <v>-2.041218369386298</v>
+        <v>-2.776688509798853</v>
       </c>
       <c r="G33">
-        <v>4.358457852512676</v>
+        <v>2.867742369997635</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.780562098638853</v>
       </c>
       <c r="E34">
-        <v>-22.41128408644797</v>
+        <v>-22.73008412811395</v>
       </c>
       <c r="F34">
-        <v>-3.091516168172028</v>
+        <v>-2.702790682162512</v>
       </c>
       <c r="G34">
-        <v>4.581658143315879</v>
+        <v>3.708445478058936</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.815074965397832</v>
       </c>
       <c r="E35">
-        <v>-19.77903158543144</v>
+        <v>-21.4381693638877</v>
       </c>
       <c r="F35">
-        <v>-2.129055135309547</v>
+        <v>-2.363475654995181</v>
       </c>
       <c r="G35">
-        <v>4.856526118350487</v>
+        <v>3.271476640693914</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.873752495613409</v>
       </c>
       <c r="E36">
-        <v>-19.11651130963526</v>
+        <v>-21.18762248246533</v>
       </c>
       <c r="F36">
-        <v>-2.303346121960771</v>
+        <v>-2.56239234779683</v>
       </c>
       <c r="G36">
-        <v>3.915543275359123</v>
+        <v>2.563665451670038</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.964764059196791</v>
       </c>
       <c r="E37">
-        <v>-19.58580159952415</v>
+        <v>-20.47819627289769</v>
       </c>
       <c r="F37">
-        <v>-2.457988233817591</v>
+        <v>-2.527044253984569</v>
       </c>
       <c r="G37">
-        <v>3.715847857884746</v>
+        <v>2.475495692322628</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.083521011673849</v>
       </c>
       <c r="E38">
-        <v>-19.27707741252523</v>
+        <v>-18.54453334314844</v>
       </c>
       <c r="F38">
-        <v>-1.942799209892286</v>
+        <v>-2.758482651020126</v>
       </c>
       <c r="G38">
-        <v>4.610800875698083</v>
+        <v>2.596271014686319</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.219264994125119</v>
       </c>
       <c r="E39">
-        <v>-17.48988344608007</v>
+        <v>-17.49973287704675</v>
       </c>
       <c r="F39">
-        <v>-2.34178899638989</v>
+        <v>-2.436159096019018</v>
       </c>
       <c r="G39">
-        <v>3.788424947742188</v>
+        <v>2.396297511386643</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.378241766621015</v>
       </c>
       <c r="E40">
-        <v>-16.57678911801747</v>
+        <v>-18.27007159049156</v>
       </c>
       <c r="F40">
-        <v>-2.269884220724685</v>
+        <v>-2.460762436249567</v>
       </c>
       <c r="G40">
-        <v>2.998667824984732</v>
+        <v>1.205577044549279</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.556936245495622</v>
       </c>
       <c r="E41">
-        <v>-15.64810325394645</v>
+        <v>-17.48812186969109</v>
       </c>
       <c r="F41">
-        <v>-1.997076327225918</v>
+        <v>-2.267660882615571</v>
       </c>
       <c r="G41">
-        <v>3.490369911750525</v>
+        <v>0.613942830135047</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.742002705072323</v>
       </c>
       <c r="E42">
-        <v>-14.69358244566168</v>
+        <v>-15.71545524786253</v>
       </c>
       <c r="F42">
-        <v>-2.22404236865376</v>
+        <v>-2.672552786858122</v>
       </c>
       <c r="G42">
-        <v>2.873459682143957</v>
+        <v>1.482699501096131</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.940317498068973</v>
       </c>
       <c r="E43">
-        <v>-14.6729326041867</v>
+        <v>-14.52654515341475</v>
       </c>
       <c r="F43">
-        <v>-1.69795368644242</v>
+        <v>-2.286541032460177</v>
       </c>
       <c r="G43">
-        <v>1.453973897451875</v>
+        <v>0.8737246491471963</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.152872967893558</v>
       </c>
       <c r="E44">
-        <v>-13.64675775167856</v>
+        <v>-14.82626220561241</v>
       </c>
       <c r="F44">
-        <v>-1.831329121967168</v>
+        <v>-2.088763344837379</v>
       </c>
       <c r="G44">
-        <v>1.104565679055037</v>
+        <v>-0.2001898394280626</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.368280562504097</v>
       </c>
       <c r="E45">
-        <v>-11.96106500164132</v>
+        <v>-13.39721166301188</v>
       </c>
       <c r="F45">
-        <v>-1.749615647885413</v>
+        <v>-2.01292216727407</v>
       </c>
       <c r="G45">
-        <v>1.897186423703962</v>
+        <v>-0.4793251076627913</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.58974799494195</v>
       </c>
       <c r="E46">
-        <v>-11.76443866022828</v>
+        <v>-11.34940401742529</v>
       </c>
       <c r="F46">
-        <v>-1.894448232958282</v>
+        <v>-2.045412393546672</v>
       </c>
       <c r="G46">
-        <v>0.6166376142040138</v>
+        <v>-0.333575029750838</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.821781392503343</v>
       </c>
       <c r="E47">
-        <v>-10.26523299830091</v>
+        <v>-11.70007545915726</v>
       </c>
       <c r="F47">
-        <v>-1.528725681357106</v>
+        <v>-1.996548657190335</v>
       </c>
       <c r="G47">
-        <v>-0.217004100222021</v>
+        <v>-1.251804493250791</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.0571199351098</v>
       </c>
       <c r="E48">
-        <v>-8.404636996665426</v>
+        <v>-11.40374570551733</v>
       </c>
       <c r="F48">
-        <v>-1.872054976958403</v>
+        <v>-2.032160171836686</v>
       </c>
       <c r="G48">
-        <v>0.6538150406100292</v>
+        <v>-1.617801855344917</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.291936286305734</v>
       </c>
       <c r="E49">
-        <v>-8.387410681540247</v>
+        <v>-10.70492518207567</v>
       </c>
       <c r="F49">
-        <v>-1.245210310809753</v>
+        <v>-1.516359812768115</v>
       </c>
       <c r="G49">
-        <v>-0.2877239740319321</v>
+        <v>-1.113049598063317</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.534502497068578</v>
       </c>
       <c r="E50">
-        <v>-8.275887952153349</v>
+        <v>-10.23411785339421</v>
       </c>
       <c r="F50">
-        <v>-1.568459152199787</v>
+        <v>-2.128618585688272</v>
       </c>
       <c r="G50">
-        <v>0.410380695470801</v>
+        <v>-1.699943111265314</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.780445699139173</v>
       </c>
       <c r="E51">
-        <v>-6.189171657892856</v>
+        <v>-7.697484081049645</v>
       </c>
       <c r="F51">
-        <v>-1.512923744781302</v>
+        <v>-1.528340490514804</v>
       </c>
       <c r="G51">
-        <v>-1.495559961307328</v>
+        <v>-2.797955060820927</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.01783510409743</v>
       </c>
       <c r="E52">
-        <v>-7.554130707862832</v>
+        <v>-6.937877851003019</v>
       </c>
       <c r="F52">
-        <v>-1.111053724824164</v>
+        <v>-1.171677793198046</v>
       </c>
       <c r="G52">
-        <v>-1.896629242844493</v>
+        <v>-2.791588881748909</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.25502110852536</v>
       </c>
       <c r="E53">
-        <v>-6.002381162024469</v>
+        <v>-7.048386202212199</v>
       </c>
       <c r="F53">
-        <v>-1.414130163221225</v>
+        <v>-1.700129807609574</v>
       </c>
       <c r="G53">
-        <v>-1.475997947715775</v>
+        <v>-3.470538734761419</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.48910493805623</v>
       </c>
       <c r="E54">
-        <v>-4.752377424739205</v>
+        <v>-6.812067786121921</v>
       </c>
       <c r="F54">
-        <v>-1.349792523780593</v>
+        <v>-1.483646755664159</v>
       </c>
       <c r="G54">
-        <v>-2.153756004334147</v>
+        <v>-4.723563668647867</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.70384865337971</v>
       </c>
       <c r="E55">
-        <v>-2.739674509660076</v>
+        <v>-6.768277442467749</v>
       </c>
       <c r="F55">
-        <v>-1.230753642896096</v>
+        <v>-1.195872748299014</v>
       </c>
       <c r="G55">
-        <v>-2.113503081122149</v>
+        <v>-3.612266499843158</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.90676713480265</v>
       </c>
       <c r="E56">
-        <v>-3.677317695318262</v>
+        <v>-5.785023466604307</v>
       </c>
       <c r="F56">
-        <v>-1.589197330128872</v>
+        <v>-1.744688518573562</v>
       </c>
       <c r="G56">
-        <v>-3.017334982071811</v>
+        <v>-4.198511146119457</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.09852647313189</v>
       </c>
       <c r="E57">
-        <v>-1.673422662184052</v>
+        <v>-5.157576221997533</v>
       </c>
       <c r="F57">
-        <v>-1.680109824218715</v>
+        <v>-1.440529403981042</v>
       </c>
       <c r="G57">
-        <v>-2.621281177026642</v>
+        <v>-4.2188478273672</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.26582292727708</v>
       </c>
       <c r="E58">
-        <v>-2.393771551058184</v>
+        <v>-3.599083778361749</v>
       </c>
       <c r="F58">
-        <v>-1.322337114582206</v>
+        <v>-1.497722374572529</v>
       </c>
       <c r="G58">
-        <v>-3.368037623774504</v>
+        <v>-4.487621088064009</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.4102227512779</v>
       </c>
       <c r="E59">
-        <v>-0.8300758907875861</v>
+        <v>-4.513939682813337</v>
       </c>
       <c r="F59">
-        <v>-1.179009673080224</v>
+        <v>-1.926947571272315</v>
       </c>
       <c r="G59">
-        <v>-2.948286933759232</v>
+        <v>-5.213868705196087</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.53558137808331</v>
       </c>
       <c r="E60">
-        <v>-0.5803667770566273</v>
+        <v>-3.821336754184202</v>
       </c>
       <c r="F60">
-        <v>-1.63859370672521</v>
+        <v>-1.51437587283841</v>
       </c>
       <c r="G60">
-        <v>-2.69314981013868</v>
+        <v>-4.945688032150806</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.6323074032416</v>
       </c>
       <c r="E61">
-        <v>-2.653592747248271</v>
+        <v>-3.857745685205872</v>
       </c>
       <c r="F61">
-        <v>-1.567706166230642</v>
+        <v>-1.685780827458281</v>
       </c>
       <c r="G61">
-        <v>-2.942404094335947</v>
+        <v>-5.173966699811251</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.6919159998118</v>
       </c>
       <c r="E62">
-        <v>0.6298588445452604</v>
+        <v>-3.112680385197876</v>
       </c>
       <c r="F62">
-        <v>-1.973023022950829</v>
+        <v>-1.538584081817823</v>
       </c>
       <c r="G62">
-        <v>-3.272177467139368</v>
+        <v>-4.613203322550723</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.72131704555635</v>
       </c>
       <c r="E63">
-        <v>-1.32594379462749</v>
+        <v>-3.096975637339275</v>
       </c>
       <c r="F63">
-        <v>-2.114609236172126</v>
+        <v>-1.451786088617685</v>
       </c>
       <c r="G63">
-        <v>-4.289746470636231</v>
+        <v>-4.630855151366116</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.71346531506292</v>
       </c>
       <c r="E64">
-        <v>0.08296409558692665</v>
+        <v>-1.670062534470361</v>
       </c>
       <c r="F64">
-        <v>-1.65437990432036</v>
+        <v>-1.705564726139341</v>
       </c>
       <c r="G64">
-        <v>-3.78582184973945</v>
+        <v>-5.064738560288538</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.65424389775823</v>
       </c>
       <c r="E65">
-        <v>0.4770953023705086</v>
+        <v>-2.03375786744839</v>
       </c>
       <c r="F65">
-        <v>-1.810991873861037</v>
+        <v>-1.532329907926686</v>
       </c>
       <c r="G65">
-        <v>-4.175443264801815</v>
+        <v>-5.078881210832304</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.55305521486434</v>
       </c>
       <c r="E66">
-        <v>1.17180397141321</v>
+        <v>-1.958548971129001</v>
       </c>
       <c r="F66">
-        <v>-1.97038384440551</v>
+        <v>-1.617514241426171</v>
       </c>
       <c r="G66">
-        <v>-3.205642122891096</v>
+        <v>-4.719220232900343</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.40828972461932</v>
       </c>
       <c r="E67">
-        <v>1.038712120327779</v>
+        <v>-1.897160977481021</v>
       </c>
       <c r="F67">
-        <v>-2.010253995869653</v>
+        <v>-2.131150076471227</v>
       </c>
       <c r="G67">
-        <v>-2.265705412290142</v>
+        <v>-4.581676997380243</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.20762642430406</v>
       </c>
       <c r="E68">
-        <v>1.936386994394266</v>
+        <v>-2.060100000751009</v>
       </c>
       <c r="F68">
-        <v>-1.967612127075743</v>
+        <v>-1.728850133832035</v>
       </c>
       <c r="G68">
-        <v>-1.976330626702447</v>
+        <v>-4.041551561011531</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.95997824150753</v>
       </c>
       <c r="E69">
-        <v>2.502799466325659</v>
+        <v>-1.771595450196338</v>
       </c>
       <c r="F69">
-        <v>-1.911612005544288</v>
+        <v>-1.710042880318876</v>
       </c>
       <c r="G69">
-        <v>-3.034486918510775</v>
+        <v>-4.439310297009425</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.66912979764815</v>
       </c>
       <c r="E70">
-        <v>0.01749141838402863</v>
+        <v>-1.012600564140748</v>
       </c>
       <c r="F70">
-        <v>-1.968524159586225</v>
+        <v>-1.908673786366558</v>
       </c>
       <c r="G70">
-        <v>-3.489153932328741</v>
+        <v>-4.413008012699915</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.32861420861377</v>
       </c>
       <c r="E71">
-        <v>0.4185149626072848</v>
+        <v>-1.225230532696902</v>
       </c>
       <c r="F71">
-        <v>-1.801415946684675</v>
+        <v>-1.985867687898638</v>
       </c>
       <c r="G71">
-        <v>-2.11154654870844</v>
+        <v>-3.64246198570685</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.942751882953354</v>
       </c>
       <c r="E72">
-        <v>0.1506874243716368</v>
+        <v>-2.123974126629199</v>
       </c>
       <c r="F72">
-        <v>-2.010686403653914</v>
+        <v>-1.86316825146117</v>
       </c>
       <c r="G72">
-        <v>-1.792979372555452</v>
+        <v>-3.381541339029192</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.521059309715376</v>
       </c>
       <c r="E73">
-        <v>-0.961202384153689</v>
+        <v>-2.155872697539229</v>
       </c>
       <c r="F73">
-        <v>-2.530255834405223</v>
+        <v>-1.784117978579416</v>
       </c>
       <c r="G73">
-        <v>-1.694354910395024</v>
+        <v>-3.15979106717219</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.063113922929055</v>
       </c>
       <c r="E74">
-        <v>0.6831318127714945</v>
+        <v>-2.601039806389256</v>
       </c>
       <c r="F74">
-        <v>-2.288946611397907</v>
+        <v>-1.849700654226455</v>
       </c>
       <c r="G74">
-        <v>-1.922802415877971</v>
+        <v>-2.786255592885143</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.568455698011856</v>
       </c>
       <c r="E75">
-        <v>-1.182898357673199</v>
+        <v>-2.693062926699125</v>
       </c>
       <c r="F75">
-        <v>-2.580836776387563</v>
+        <v>-1.462971533657687</v>
       </c>
       <c r="G75">
-        <v>-1.60675125433483</v>
+        <v>-2.301316950656082</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.052715606180968</v>
       </c>
       <c r="E76">
-        <v>0.1854842186465759</v>
+        <v>-4.088774843655191</v>
       </c>
       <c r="F76">
-        <v>-2.141165038371073</v>
+        <v>-1.71837377128883</v>
       </c>
       <c r="G76">
-        <v>-0.2702310514024231</v>
+        <v>-1.880990225716976</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.519581871353019</v>
       </c>
       <c r="E77">
-        <v>-2.207257292104265</v>
+        <v>-3.474650369578983</v>
       </c>
       <c r="F77">
-        <v>-2.08517734235066</v>
+        <v>-2.154486014575491</v>
       </c>
       <c r="G77">
-        <v>-1.271138079200135</v>
+        <v>-1.492868487783901</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.968048806855411</v>
       </c>
       <c r="E78">
-        <v>-1.886949268593725</v>
+        <v>-5.461867032942942</v>
       </c>
       <c r="F78">
-        <v>-2.562685589857421</v>
+        <v>-2.343642882637356</v>
       </c>
       <c r="G78">
-        <v>0.3230584357814449</v>
+        <v>-1.164333259012168</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.415219944657452</v>
       </c>
       <c r="E79">
-        <v>-2.19297901355808</v>
+        <v>-4.667572691997562</v>
       </c>
       <c r="F79">
-        <v>-2.491385522396259</v>
+        <v>-2.523647947633091</v>
       </c>
       <c r="G79">
-        <v>0.9625035488738317</v>
+        <v>-1.390277992067426</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.869403128863908</v>
       </c>
       <c r="E80">
-        <v>-1.70752207146181</v>
+        <v>-5.267101894347048</v>
       </c>
       <c r="F80">
-        <v>-2.650466855164682</v>
+        <v>-2.099273670444099</v>
       </c>
       <c r="G80">
-        <v>2.334929928725173</v>
+        <v>-0.2326696017138522</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.331902791212625</v>
       </c>
       <c r="E81">
-        <v>-3.852053393378231</v>
+        <v>-5.966900568174371</v>
       </c>
       <c r="F81">
-        <v>-2.897566366317565</v>
+        <v>-2.471833566587982</v>
       </c>
       <c r="G81">
-        <v>1.632144147829911</v>
+        <v>-0.06975765572631709</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.817580562655524</v>
       </c>
       <c r="E82">
-        <v>-4.865127370582181</v>
+        <v>-8.077966467174109</v>
       </c>
       <c r="F82">
-        <v>-2.758179468550701</v>
+        <v>-1.939520531712006</v>
       </c>
       <c r="G82">
-        <v>1.769528477164126</v>
+        <v>0.837037183480993</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.338982395842559</v>
       </c>
       <c r="E83">
-        <v>-7.479016909497604</v>
+        <v>-8.040153709210061</v>
       </c>
       <c r="F83">
-        <v>-2.847606699887325</v>
+        <v>-2.657135212757217</v>
       </c>
       <c r="G83">
-        <v>3.341931670860683</v>
+        <v>1.91718211876116</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.901471232727621</v>
       </c>
       <c r="E84">
-        <v>-7.415794883876518</v>
+        <v>-9.472935714392916</v>
       </c>
       <c r="F84">
-        <v>-2.563894177898105</v>
+        <v>-2.652715872663282</v>
       </c>
       <c r="G84">
-        <v>1.931397601306791</v>
+        <v>1.394152339557245</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.518827832000055</v>
       </c>
       <c r="E85">
-        <v>-8.950535481342071</v>
+        <v>-10.3856043658988</v>
       </c>
       <c r="F85">
-        <v>-3.276044947554452</v>
+        <v>-2.660339337871246</v>
       </c>
       <c r="G85">
-        <v>3.500897446565407</v>
+        <v>2.411565747413762</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.211109755518486</v>
       </c>
       <c r="E86">
-        <v>-11.54900556626138</v>
+        <v>-11.62428691816489</v>
       </c>
       <c r="F86">
-        <v>-3.285142078371996</v>
+        <v>-3.003614789591361</v>
       </c>
       <c r="G86">
-        <v>2.107952305461662</v>
+        <v>2.310792741198347</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.987981023004708</v>
       </c>
       <c r="E87">
-        <v>-11.50390649361899</v>
+        <v>-12.74243054929481</v>
       </c>
       <c r="F87">
-        <v>-2.808624558278983</v>
+        <v>-2.931968464555829</v>
       </c>
       <c r="G87">
-        <v>4.305783762437332</v>
+        <v>2.588352189756383</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.855990864018242</v>
       </c>
       <c r="E88">
-        <v>-12.08986838784149</v>
+        <v>-14.41771233758841</v>
       </c>
       <c r="F88">
-        <v>-3.110995227648858</v>
+        <v>-2.740654527777075</v>
       </c>
       <c r="G88">
-        <v>3.737326677343538</v>
+        <v>3.201332801807836</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.833280145863601</v>
       </c>
       <c r="E89">
-        <v>-15.08958844068444</v>
+        <v>-15.26570079484274</v>
       </c>
       <c r="F89">
-        <v>-3.315139747129574</v>
+        <v>-3.046877105569968</v>
       </c>
       <c r="G89">
-        <v>4.018603868542175</v>
+        <v>2.728262465337062</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.925180444936565</v>
       </c>
       <c r="E90">
-        <v>-15.79664625834606</v>
+        <v>-16.02193784022766</v>
       </c>
       <c r="F90">
-        <v>-3.304174647818717</v>
+        <v>-2.926286692540027</v>
       </c>
       <c r="G90">
-        <v>3.631372667359163</v>
+        <v>3.152697577290403</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.127426007998423</v>
       </c>
       <c r="E91">
-        <v>-18.36504274738042</v>
+        <v>-19.19085526741919</v>
       </c>
       <c r="F91">
-        <v>-3.416584932746013</v>
+        <v>-3.196196956863802</v>
       </c>
       <c r="G91">
-        <v>4.455632295726903</v>
+        <v>3.118410257140171</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.449296611691625</v>
       </c>
       <c r="E92">
-        <v>-19.27434674269861</v>
+        <v>-20.78068475118805</v>
       </c>
       <c r="F92">
-        <v>-2.994517658773817</v>
+        <v>-2.860499410144496</v>
       </c>
       <c r="G92">
-        <v>3.272711474180062</v>
+        <v>2.774689555979801</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.890082212856194</v>
       </c>
       <c r="E93">
-        <v>-21.46053549701159</v>
+        <v>-22.72723571796313</v>
       </c>
       <c r="F93">
-        <v>-2.93820027252709</v>
+        <v>-2.872497483606644</v>
       </c>
       <c r="G93">
-        <v>2.935201356451365</v>
+        <v>3.396350418435223</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.432741313010376</v>
       </c>
       <c r="E94">
-        <v>-24.14425410512528</v>
+        <v>-25.00568307323438</v>
       </c>
       <c r="F94">
-        <v>-2.784072576827408</v>
+        <v>-2.950132076597014</v>
       </c>
       <c r="G94">
-        <v>1.786402327777791</v>
+        <v>2.653189224143009</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.072834248931152</v>
       </c>
       <c r="E95">
-        <v>-25.79591990146889</v>
+        <v>-26.47813451072443</v>
       </c>
       <c r="F95">
-        <v>-3.333893985128955</v>
+        <v>-3.368552048894683</v>
       </c>
       <c r="G95">
-        <v>2.513249153652477</v>
+        <v>2.152770470972316</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.80489639431001</v>
       </c>
       <c r="E96">
-        <v>-28.94694985633012</v>
+        <v>-28.22197739549416</v>
       </c>
       <c r="F96">
-        <v>-3.902966651871562</v>
+        <v>-3.44887552247454</v>
       </c>
       <c r="G96">
-        <v>1.784720570643842</v>
+        <v>2.398982363818992</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.595574708161989</v>
       </c>
       <c r="E97">
-        <v>-29.62154304383075</v>
+        <v>-31.13310464708804</v>
       </c>
       <c r="F97">
-        <v>-3.569574451634248</v>
+        <v>-3.491884358027891</v>
       </c>
       <c r="G97">
-        <v>0.8073250372660341</v>
+        <v>1.954581351718307</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.442635834637329</v>
       </c>
       <c r="E98">
-        <v>-34.14942608564311</v>
+        <v>-33.59128260724972</v>
       </c>
       <c r="F98">
-        <v>-3.23848345604191</v>
+        <v>-3.5176598381334</v>
       </c>
       <c r="G98">
-        <v>1.267831853415274</v>
+        <v>0.9383531191648484</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.304144701136241</v>
       </c>
       <c r="E99">
-        <v>-34.41395463056417</v>
+        <v>-34.96266529759958</v>
       </c>
       <c r="F99">
-        <v>-3.971167796878851</v>
+        <v>-3.339763796545192</v>
       </c>
       <c r="G99">
-        <v>1.164360752585353</v>
+        <v>1.564317690821323</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.194367714425818</v>
       </c>
       <c r="E100">
-        <v>-38.12951547640661</v>
+        <v>-37.71515104775676</v>
       </c>
       <c r="F100">
-        <v>-3.678367256113518</v>
+        <v>-3.582628693534965</v>
       </c>
       <c r="G100">
-        <v>0.09681575362765195</v>
+        <v>0.09528959213404793</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.02315736152552</v>
       </c>
       <c r="E101">
-        <v>-41.70771638441139</v>
+        <v>-39.2994218296812</v>
       </c>
       <c r="F101">
-        <v>-3.792102928885293</v>
+        <v>-3.645380837766639</v>
       </c>
       <c r="G101">
-        <v>0.2419566911603793</v>
+        <v>0.698308772657834</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.88608977506609</v>
       </c>
       <c r="E102">
-        <v>-42.4337779432462</v>
+        <v>-42.02679945570285</v>
       </c>
       <c r="F102">
-        <v>-4.070832820946674</v>
+        <v>-3.795374151758948</v>
       </c>
       <c r="G102">
-        <v>-0.5746555770116444</v>
+        <v>0.03616655934820381</v>
       </c>
     </row>
   </sheetData>
